--- a/HV_gamma.xlsx
+++ b/HV_gamma.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\代码\MOEA\Platemohjp\PlatEMO-master\PlatEMO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\论文\MOPSO_PPHS\1.experiments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49E2836F-C2AB-49E9-8F85-8D254A895193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BED120B-C604-4F4C-8928-19640AC0FE86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4920" yWindow="3150" windowWidth="19200" windowHeight="10050" xr2:uid="{607F62B6-7C41-485C-A2FE-5B2760F19439}"/>
+    <workbookView xWindow="-24240" yWindow="1965" windowWidth="19200" windowHeight="10050" xr2:uid="{607F62B6-7C41-485C-A2FE-5B2760F19439}"/>
   </bookViews>
   <sheets>
     <sheet name="HV" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="131">
   <si>
     <t>Problem</t>
   </si>
@@ -56,9 +56,6 @@
     <t>gamma05</t>
   </si>
   <si>
-    <t>gamma1</t>
-  </si>
-  <si>
     <t>gamma2</t>
   </si>
   <si>
@@ -77,9 +74,6 @@
     <t>8.2030e-1 (4.35e-2) =</t>
   </si>
   <si>
-    <t>8.2919e-1 (4.69e-2) =</t>
-  </si>
-  <si>
     <t>8.4392e-1 (4.38e-2) =</t>
   </si>
   <si>
@@ -98,9 +92,6 @@
     <t>7.3536e-1 (3.53e-2) =</t>
   </si>
   <si>
-    <t>7.2723e-1 (3.67e-2) =</t>
-  </si>
-  <si>
     <t>7.4450e-1 (3.54e-2) =</t>
   </si>
   <si>
@@ -119,9 +110,6 @@
     <t>9.1120e-1 (1.24e-2) =</t>
   </si>
   <si>
-    <t>9.1064e-1 (1.35e-2) =</t>
-  </si>
-  <si>
     <t>9.0826e-1 (1.51e-3) =</t>
   </si>
   <si>
@@ -140,9 +128,6 @@
     <t>9.8480e-1 (5.23e-4) =</t>
   </si>
   <si>
-    <t>9.8507e-1 (6.22e-4) =</t>
-  </si>
-  <si>
     <t>9.8507e-1 (5.99e-4) =</t>
   </si>
   <si>
@@ -161,9 +146,6 @@
     <t>9.7152e-1 (2.37e-2) =</t>
   </si>
   <si>
-    <t>9.7296e-1 (2.16e-2) =</t>
-  </si>
-  <si>
     <t>9.7741e-1 (1.59e-2) =</t>
   </si>
   <si>
@@ -182,9 +164,6 @@
     <t>9.8416e-1 (3.87e-4) =</t>
   </si>
   <si>
-    <t>9.8413e-1 (3.35e-4) =</t>
-  </si>
-  <si>
     <t>9.8421e-1 (5.53e-4) =</t>
   </si>
   <si>
@@ -203,9 +182,6 @@
     <t>9.0481e-1 (1.88e-2) =</t>
   </si>
   <si>
-    <t>9.0361e-1 (1.77e-2) =</t>
-  </si>
-  <si>
     <t>9.0639e-1 (1.96e-2) =</t>
   </si>
   <si>
@@ -224,9 +200,6 @@
     <t>9.8523e-1 (1.08e-3) =</t>
   </si>
   <si>
-    <t>9.8528e-1 (8.45e-4) =</t>
-  </si>
-  <si>
     <t>9.8560e-1 (1.09e-3) =</t>
   </si>
   <si>
@@ -245,9 +218,6 @@
     <t>9.8412e-1 (5.27e-4) =</t>
   </si>
   <si>
-    <t>9.8409e-1 (3.61e-4) =</t>
-  </si>
-  <si>
     <t>9.8405e-1 (5.39e-4) =</t>
   </si>
   <si>
@@ -266,9 +236,6 @@
     <t>9.8357e-1 (3.46e-4) -</t>
   </si>
   <si>
-    <t>9.8352e-1 (3.16e-4) -</t>
-  </si>
-  <si>
     <t>9.8346e-1 (3.20e-4) -</t>
   </si>
   <si>
@@ -287,9 +254,6 @@
     <t>8.3059e-1 (2.10e-2) -</t>
   </si>
   <si>
-    <t>8.3332e-1 (2.16e-2) -</t>
-  </si>
-  <si>
     <t>8.3174e-1 (2.12e-2) -</t>
   </si>
   <si>
@@ -308,9 +272,6 @@
     <t>9.7108e-1 (3.08e-4) -</t>
   </si>
   <si>
-    <t>9.7107e-1 (2.99e-4) -</t>
-  </si>
-  <si>
     <t>9.7103e-1 (3.00e-4) -</t>
   </si>
   <si>
@@ -329,9 +290,6 @@
     <t>5.5305e-1 (4.76e-2) -</t>
   </si>
   <si>
-    <t>5.6290e-1 (4.27e-2) -</t>
-  </si>
-  <si>
     <t>5.6616e-1 (4.04e-2) -</t>
   </si>
   <si>
@@ -347,9 +305,6 @@
     <t>8.5574e-1 (2.69e-4) -</t>
   </si>
   <si>
-    <t>8.5592e-1 (3.61e-4) -</t>
-  </si>
-  <si>
     <t>8.5586e-1 (3.03e-4) -</t>
   </si>
   <si>
@@ -368,9 +323,6 @@
     <t>9.8341e-1 (3.36e-4) -</t>
   </si>
   <si>
-    <t>9.8338e-1 (3.34e-4) -</t>
-  </si>
-  <si>
     <t>9.8331e-1 (2.91e-4) -</t>
   </si>
   <si>
@@ -389,9 +341,6 @@
     <t>8.9422e-1 (3.49e-4) -</t>
   </si>
   <si>
-    <t>8.9433e-1 (4.34e-4) -</t>
-  </si>
-  <si>
     <t>8.9425e-1 (3.23e-4) -</t>
   </si>
   <si>
@@ -410,9 +359,6 @@
     <t>6.3979e-1 (2.40e-2) -</t>
   </si>
   <si>
-    <t>6.3957e-1 (2.03e-2) -</t>
-  </si>
-  <si>
     <t>6.3977e-1 (2.06e-2) -</t>
   </si>
   <si>
@@ -431,9 +377,6 @@
     <t>7.5694e-1 (2.90e-2) -</t>
   </si>
   <si>
-    <t>7.5065e-1 (2.31e-2) -</t>
-  </si>
-  <si>
     <t>7.5695e-1 (2.35e-2) -</t>
   </si>
   <si>
@@ -452,9 +395,6 @@
     <t>7.7291e-1 (1.81e-2) -</t>
   </si>
   <si>
-    <t>7.6773e-1 (2.86e-2) -</t>
-  </si>
-  <si>
     <t>7.7146e-1 (2.81e-2) -</t>
   </si>
   <si>
@@ -473,9 +413,6 @@
     <t>6.2165e-1 (2.66e-2) -</t>
   </si>
   <si>
-    <t>6.2695e-1 (2.20e-2) =</t>
-  </si>
-  <si>
     <t>6.1647e-1 (2.70e-2) -</t>
   </si>
   <si>
@@ -492,9 +429,6 @@
   </si>
   <si>
     <t>0/11/9</t>
-  </si>
-  <si>
-    <t>0/10/10</t>
   </si>
   <si>
     <t/>
@@ -920,15 +854,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18A924DD-925C-42C5-94FB-6244FD648BE5}">
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.625" customWidth="1"/>
     <col min="2" max="3" width="6.625" customWidth="1"/>
-    <col min="4" max="9" width="22.625" customWidth="1"/>
+    <col min="4" max="8" width="22.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -953,13 +887,10 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="B2" s="1">
         <v>2</v>
@@ -968,27 +899,24 @@
         <v>10367</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="15" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
@@ -997,27 +925,24 @@
         <v>7129</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="15" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -1026,27 +951,24 @@
         <v>2000</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="H4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="1" t="s">
+    </row>
+    <row r="5" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="15" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
@@ -1055,27 +977,24 @@
         <v>7130</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="1" t="s">
+    </row>
+    <row r="6" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="15" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
@@ -1084,27 +1003,24 @@
         <v>5327</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="B7" s="1">
         <v>2</v>
@@ -1113,27 +1029,24 @@
         <v>11225</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+        <v>41</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B8" s="1">
         <v>2</v>
@@ -1142,27 +1055,24 @@
         <v>10509</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+        <v>48</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B9" s="1">
         <v>2</v>
@@ -1171,27 +1081,24 @@
         <v>2308</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="B10" s="1">
         <v>2</v>
@@ -1200,27 +1107,24 @@
         <v>12533</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B11" s="1">
         <v>2</v>
@@ -1229,27 +1133,24 @@
         <v>24526</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+        <v>66</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="B12" s="1">
         <v>2</v>
@@ -1258,27 +1159,24 @@
         <v>22277</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+        <v>72</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="B13" s="1">
         <v>2</v>
@@ -1287,27 +1185,24 @@
         <v>22277</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+        <v>78</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="B14" s="1">
         <v>2</v>
@@ -1316,27 +1211,24 @@
         <v>22283</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+        <v>83</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="B15" s="1">
         <v>2</v>
@@ -1345,27 +1237,24 @@
         <v>22283</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+        <v>89</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="B16" s="1">
         <v>2</v>
@@ -1374,27 +1263,24 @@
         <v>29148</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+        <v>95</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="B17" s="1">
         <v>2</v>
@@ -1403,27 +1289,24 @@
         <v>22283</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+        <v>101</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="B18" s="1">
         <v>2</v>
@@ -1432,27 +1315,24 @@
         <v>22283</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B19" s="1">
         <v>2</v>
@@ -1461,27 +1341,24 @@
         <v>12625</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+        <v>113</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="B20" s="1">
         <v>2</v>
@@ -1490,27 +1367,24 @@
         <v>12620</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+        <v>119</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="B21" s="1">
         <v>2</v>
@@ -1519,47 +1393,41 @@
         <v>12646</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="15" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>152</v>
+        <v>125</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>130</v>
       </c>
     </row>
   </sheetData>
